--- a/files/bulk.xlsx
+++ b/files/bulk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\system\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9685EC0D-22E5-4159-B711-AFA067AF66C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69A9D27-FFC4-44CE-AD46-5A1D030EC359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10744,7 +10744,7 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>12345678</v>
@@ -10776,7 +10776,7 @@
         <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>12345678</v>
@@ -10808,7 +10808,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>12345678</v>
@@ -10840,7 +10840,7 @@
         <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>12345678</v>
@@ -10872,7 +10872,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>12345678</v>
@@ -10904,7 +10904,7 @@
         <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E17">
         <v>12345678</v>
@@ -10936,7 +10936,7 @@
         <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E18">
         <v>12345678</v>
@@ -10968,7 +10968,7 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <v>12345678</v>
@@ -11000,7 +11000,7 @@
         <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>12345678</v>
@@ -11032,7 +11032,7 @@
         <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>12345678</v>
@@ -11192,7 +11192,7 @@
         <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>12345678</v>
@@ -11224,7 +11224,7 @@
         <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>12345678</v>
@@ -11256,7 +11256,7 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>12345678</v>
@@ -11288,7 +11288,7 @@
         <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>12345678</v>
@@ -11384,7 +11384,7 @@
         <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>12345678</v>
@@ -11416,7 +11416,7 @@
         <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>12345678</v>
@@ -11512,7 +11512,7 @@
         <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>12345678</v>
@@ -11544,7 +11544,7 @@
         <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E37">
         <v>12345678</v>
@@ -11576,7 +11576,7 @@
         <v>46</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E38">
         <v>12345678</v>
@@ -11608,7 +11608,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E39">
         <v>12345678</v>
@@ -11640,7 +11640,7 @@
         <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E40">
         <v>12345678</v>
@@ -11800,7 +11800,7 @@
         <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>12345678</v>
@@ -11832,7 +11832,7 @@
         <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E46">
         <v>12345678</v>
@@ -11992,7 +11992,7 @@
         <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E51">
         <v>12345678</v>
@@ -12024,7 +12024,7 @@
         <v>46</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E52">
         <v>12345678</v>
@@ -12184,7 +12184,7 @@
         <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E57">
         <v>12345678</v>
@@ -12216,7 +12216,7 @@
         <v>46</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E58">
         <v>12345678</v>
@@ -12376,7 +12376,7 @@
         <v>46</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E63">
         <v>12345678</v>
@@ -12408,7 +12408,7 @@
         <v>46</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E64">
         <v>12345678</v>
@@ -12568,7 +12568,7 @@
         <v>46</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E69">
         <v>12345678</v>
@@ -12600,7 +12600,7 @@
         <v>46</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E70">
         <v>12345678</v>
@@ -12760,7 +12760,7 @@
         <v>46</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E75">
         <v>12345678</v>
@@ -12792,7 +12792,7 @@
         <v>46</v>
       </c>
       <c r="D76" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>12345678</v>
@@ -12952,7 +12952,7 @@
         <v>46</v>
       </c>
       <c r="D81" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E81">
         <v>12345678</v>
@@ -12984,7 +12984,7 @@
         <v>46</v>
       </c>
       <c r="D82" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E82">
         <v>12345678</v>
@@ -13144,7 +13144,7 @@
         <v>46</v>
       </c>
       <c r="D87" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E87">
         <v>12345678</v>
@@ -13176,7 +13176,7 @@
         <v>46</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E88">
         <v>12345678</v>
@@ -13295,7 +13295,7 @@
         <v>298</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E92">
         <v>12345678</v>
@@ -13324,7 +13324,7 @@
         <v>298</v>
       </c>
       <c r="D93" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E93">
         <v>12345678</v>
@@ -13353,7 +13353,7 @@
         <v>298</v>
       </c>
       <c r="D94" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E94">
         <v>12345678</v>
@@ -13382,7 +13382,7 @@
         <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E95">
         <v>12345678</v>
@@ -13411,7 +13411,7 @@
         <v>298</v>
       </c>
       <c r="D96" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E96">
         <v>12345678</v>
@@ -13440,7 +13440,7 @@
         <v>298</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E97">
         <v>12345678</v>
@@ -13469,7 +13469,7 @@
         <v>298</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E98">
         <v>12345678</v>
@@ -13498,7 +13498,7 @@
         <v>298</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E99">
         <v>12345678</v>
@@ -13527,7 +13527,7 @@
         <v>298</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E100">
         <v>12345678</v>
@@ -13556,7 +13556,7 @@
         <v>298</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E101">
         <v>12345678</v>
@@ -13759,7 +13759,7 @@
         <v>298</v>
       </c>
       <c r="D108" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E108">
         <v>12345678</v>
@@ -13788,7 +13788,7 @@
         <v>298</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E109">
         <v>12345678</v>
@@ -13817,7 +13817,7 @@
         <v>298</v>
       </c>
       <c r="D110" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E110">
         <v>12345678</v>
@@ -13846,7 +13846,7 @@
         <v>298</v>
       </c>
       <c r="D111" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E111">
         <v>12345678</v>
@@ -13875,7 +13875,7 @@
         <v>298</v>
       </c>
       <c r="D112" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E112">
         <v>12345678</v>
@@ -13904,7 +13904,7 @@
         <v>298</v>
       </c>
       <c r="D113" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E113">
         <v>12345678</v>
@@ -13933,7 +13933,7 @@
         <v>298</v>
       </c>
       <c r="D114" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E114">
         <v>12345678</v>
@@ -13962,7 +13962,7 @@
         <v>298</v>
       </c>
       <c r="D115" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E115">
         <v>12345678</v>
@@ -13991,7 +13991,7 @@
         <v>298</v>
       </c>
       <c r="D116" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E116">
         <v>12345678</v>
@@ -14020,7 +14020,7 @@
         <v>298</v>
       </c>
       <c r="D117" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E117">
         <v>12345678</v>
@@ -14223,7 +14223,7 @@
         <v>298</v>
       </c>
       <c r="D124" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E124">
         <v>12345678</v>
@@ -14252,7 +14252,7 @@
         <v>298</v>
       </c>
       <c r="D125" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E125">
         <v>12345678</v>
@@ -14281,7 +14281,7 @@
         <v>298</v>
       </c>
       <c r="D126" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E126">
         <v>12345678</v>
@@ -14310,7 +14310,7 @@
         <v>298</v>
       </c>
       <c r="D127" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E127">
         <v>12345678</v>
@@ -14339,7 +14339,7 @@
         <v>298</v>
       </c>
       <c r="D128" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E128">
         <v>12345678</v>
@@ -14368,7 +14368,7 @@
         <v>298</v>
       </c>
       <c r="D129" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E129">
         <v>12345678</v>
@@ -14397,7 +14397,7 @@
         <v>298</v>
       </c>
       <c r="D130" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E130">
         <v>12345678</v>
@@ -14426,7 +14426,7 @@
         <v>298</v>
       </c>
       <c r="D131" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E131">
         <v>12345678</v>
@@ -14455,7 +14455,7 @@
         <v>298</v>
       </c>
       <c r="D132" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E132">
         <v>12345678</v>
@@ -14484,7 +14484,7 @@
         <v>298</v>
       </c>
       <c r="D133" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E133">
         <v>12345678</v>
@@ -14687,7 +14687,7 @@
         <v>298</v>
       </c>
       <c r="D140" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E140">
         <v>12345678</v>
@@ -14716,7 +14716,7 @@
         <v>298</v>
       </c>
       <c r="D141" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E141">
         <v>12345678</v>
@@ -14745,7 +14745,7 @@
         <v>298</v>
       </c>
       <c r="D142" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E142">
         <v>12345678</v>
@@ -14774,7 +14774,7 @@
         <v>298</v>
       </c>
       <c r="D143" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E143">
         <v>12345678</v>
@@ -14803,7 +14803,7 @@
         <v>298</v>
       </c>
       <c r="D144" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E144">
         <v>12345678</v>
@@ -14832,7 +14832,7 @@
         <v>298</v>
       </c>
       <c r="D145" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E145">
         <v>12345678</v>
@@ -14861,7 +14861,7 @@
         <v>298</v>
       </c>
       <c r="D146" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E146">
         <v>12345678</v>
@@ -14890,7 +14890,7 @@
         <v>298</v>
       </c>
       <c r="D147" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E147">
         <v>12345678</v>
@@ -14919,7 +14919,7 @@
         <v>298</v>
       </c>
       <c r="D148" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E148">
         <v>12345678</v>
@@ -14948,7 +14948,7 @@
         <v>298</v>
       </c>
       <c r="D149" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E149">
         <v>12345678</v>
@@ -16601,7 +16601,7 @@
         <v>298</v>
       </c>
       <c r="D206" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E206">
         <v>12345678</v>
@@ -16630,7 +16630,7 @@
         <v>298</v>
       </c>
       <c r="D207" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E207">
         <v>12345678</v>
@@ -16775,7 +16775,7 @@
         <v>298</v>
       </c>
       <c r="D212" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E212">
         <v>12345678</v>
@@ -16804,7 +16804,7 @@
         <v>298</v>
       </c>
       <c r="D213" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E213">
         <v>12345678</v>
@@ -16949,7 +16949,7 @@
         <v>298</v>
       </c>
       <c r="D218" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E218">
         <v>12345678</v>
@@ -16978,7 +16978,7 @@
         <v>298</v>
       </c>
       <c r="D219" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E219">
         <v>12345678</v>
@@ -17123,7 +17123,7 @@
         <v>298</v>
       </c>
       <c r="D224" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E224">
         <v>12345678</v>
@@ -17152,7 +17152,7 @@
         <v>298</v>
       </c>
       <c r="D225" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E225">
         <v>12345678</v>
@@ -17297,7 +17297,7 @@
         <v>298</v>
       </c>
       <c r="D230" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E230">
         <v>12345678</v>
@@ -17326,7 +17326,7 @@
         <v>298</v>
       </c>
       <c r="D231" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E231">
         <v>12345678</v>
@@ -17471,7 +17471,7 @@
         <v>298</v>
       </c>
       <c r="D236" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E236">
         <v>12345678</v>
@@ -17500,7 +17500,7 @@
         <v>298</v>
       </c>
       <c r="D237" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E237">
         <v>12345678</v>
@@ -17645,7 +17645,7 @@
         <v>298</v>
       </c>
       <c r="D242" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E242">
         <v>12345678</v>
@@ -17674,7 +17674,7 @@
         <v>298</v>
       </c>
       <c r="D243" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E243">
         <v>12345678</v>
@@ -17819,7 +17819,7 @@
         <v>298</v>
       </c>
       <c r="D248" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E248">
         <v>12345678</v>
@@ -17848,7 +17848,7 @@
         <v>298</v>
       </c>
       <c r="D249" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E249">
         <v>12345678</v>
@@ -17993,7 +17993,7 @@
         <v>298</v>
       </c>
       <c r="D254" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E254">
         <v>12345678</v>
@@ -18022,7 +18022,7 @@
         <v>298</v>
       </c>
       <c r="D255" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E255">
         <v>12345678</v>
@@ -18167,7 +18167,7 @@
         <v>298</v>
       </c>
       <c r="D260" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E260">
         <v>12345678</v>
@@ -18196,7 +18196,7 @@
         <v>298</v>
       </c>
       <c r="D261" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E261">
         <v>12345678</v>
@@ -18341,7 +18341,7 @@
         <v>298</v>
       </c>
       <c r="D266" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E266">
         <v>12345678</v>
@@ -18370,7 +18370,7 @@
         <v>298</v>
       </c>
       <c r="D267" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E267">
         <v>12345678</v>
@@ -18515,7 +18515,7 @@
         <v>298</v>
       </c>
       <c r="D272" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E272">
         <v>12345678</v>
@@ -18544,7 +18544,7 @@
         <v>298</v>
       </c>
       <c r="D273" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E273">
         <v>12345678</v>
@@ -18689,7 +18689,7 @@
         <v>298</v>
       </c>
       <c r="D278" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E278">
         <v>12345678</v>
@@ -18718,7 +18718,7 @@
         <v>298</v>
       </c>
       <c r="D279" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E279">
         <v>12345678</v>
@@ -18863,7 +18863,7 @@
         <v>298</v>
       </c>
       <c r="D284" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E284">
         <v>12345678</v>
@@ -18892,7 +18892,7 @@
         <v>298</v>
       </c>
       <c r="D285" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E285">
         <v>12345678</v>
@@ -19037,7 +19037,7 @@
         <v>298</v>
       </c>
       <c r="D290" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E290">
         <v>12345678</v>
@@ -19066,7 +19066,7 @@
         <v>298</v>
       </c>
       <c r="D291" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E291">
         <v>12345678</v>
@@ -19211,7 +19211,7 @@
         <v>298</v>
       </c>
       <c r="D296" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E296">
         <v>12345678</v>
@@ -19240,7 +19240,7 @@
         <v>298</v>
       </c>
       <c r="D297" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E297">
         <v>12345678</v>
@@ -19385,7 +19385,7 @@
         <v>298</v>
       </c>
       <c r="D302" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E302">
         <v>12345678</v>
@@ -19414,7 +19414,7 @@
         <v>298</v>
       </c>
       <c r="D303" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E303">
         <v>12345678</v>
@@ -19559,7 +19559,7 @@
         <v>298</v>
       </c>
       <c r="D308" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E308">
         <v>12345678</v>
@@ -19588,7 +19588,7 @@
         <v>298</v>
       </c>
       <c r="D309" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E309">
         <v>12345678</v>
@@ -19733,7 +19733,7 @@
         <v>298</v>
       </c>
       <c r="D314" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E314">
         <v>12345678</v>
@@ -19762,7 +19762,7 @@
         <v>298</v>
       </c>
       <c r="D315" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E315">
         <v>12345678</v>
@@ -19907,7 +19907,7 @@
         <v>298</v>
       </c>
       <c r="D320" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E320">
         <v>12345678</v>
@@ -19936,7 +19936,7 @@
         <v>298</v>
       </c>
       <c r="D321" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E321">
         <v>12345678</v>
@@ -20081,7 +20081,7 @@
         <v>298</v>
       </c>
       <c r="D326" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E326">
         <v>12345678</v>
@@ -20110,7 +20110,7 @@
         <v>298</v>
       </c>
       <c r="D327" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E327">
         <v>12345678</v>
@@ -20255,7 +20255,7 @@
         <v>298</v>
       </c>
       <c r="D332" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E332">
         <v>12345678</v>
@@ -20284,7 +20284,7 @@
         <v>298</v>
       </c>
       <c r="D333" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E333">
         <v>12345678</v>
@@ -20429,7 +20429,7 @@
         <v>298</v>
       </c>
       <c r="D338" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E338">
         <v>12345678</v>
@@ -20458,7 +20458,7 @@
         <v>298</v>
       </c>
       <c r="D339" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E339">
         <v>12345678</v>
@@ -20603,7 +20603,7 @@
         <v>298</v>
       </c>
       <c r="D344" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E344">
         <v>12345678</v>
@@ -20632,7 +20632,7 @@
         <v>298</v>
       </c>
       <c r="D345" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E345">
         <v>12345678</v>
@@ -20777,7 +20777,7 @@
         <v>298</v>
       </c>
       <c r="D350" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E350">
         <v>12345678</v>
@@ -20806,7 +20806,7 @@
         <v>298</v>
       </c>
       <c r="D351" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E351">
         <v>12345678</v>
@@ -20951,7 +20951,7 @@
         <v>298</v>
       </c>
       <c r="D356" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E356">
         <v>12345678</v>
@@ -20980,7 +20980,7 @@
         <v>298</v>
       </c>
       <c r="D357" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E357">
         <v>12345678</v>
@@ -21125,7 +21125,7 @@
         <v>298</v>
       </c>
       <c r="D362" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E362">
         <v>12345678</v>
@@ -21154,7 +21154,7 @@
         <v>298</v>
       </c>
       <c r="D363" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E363">
         <v>12345678</v>
@@ -21299,7 +21299,7 @@
         <v>298</v>
       </c>
       <c r="D368" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E368">
         <v>12345678</v>
@@ -21328,7 +21328,7 @@
         <v>298</v>
       </c>
       <c r="D369" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E369">
         <v>12345678</v>
@@ -21473,7 +21473,7 @@
         <v>298</v>
       </c>
       <c r="D374" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E374">
         <v>12345678</v>
@@ -21502,7 +21502,7 @@
         <v>298</v>
       </c>
       <c r="D375" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E375">
         <v>12345678</v>
@@ -21647,7 +21647,7 @@
         <v>298</v>
       </c>
       <c r="D380" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E380">
         <v>12345678</v>
@@ -21676,7 +21676,7 @@
         <v>298</v>
       </c>
       <c r="D381" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E381">
         <v>12345678</v>
@@ -21821,7 +21821,7 @@
         <v>298</v>
       </c>
       <c r="D386" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E386">
         <v>12345678</v>
@@ -21850,7 +21850,7 @@
         <v>298</v>
       </c>
       <c r="D387" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E387">
         <v>12345678</v>
@@ -21995,7 +21995,7 @@
         <v>298</v>
       </c>
       <c r="D392" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E392">
         <v>12345678</v>
@@ -22024,7 +22024,7 @@
         <v>298</v>
       </c>
       <c r="D393" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E393">
         <v>12345678</v>
@@ -22169,7 +22169,7 @@
         <v>298</v>
       </c>
       <c r="D398" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E398">
         <v>12345678</v>
@@ -22198,7 +22198,7 @@
         <v>298</v>
       </c>
       <c r="D399" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E399">
         <v>12345678</v>
@@ -22343,7 +22343,7 @@
         <v>298</v>
       </c>
       <c r="D404" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E404">
         <v>12345678</v>
@@ -22372,7 +22372,7 @@
         <v>298</v>
       </c>
       <c r="D405" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E405">
         <v>12345678</v>
@@ -22517,7 +22517,7 @@
         <v>298</v>
       </c>
       <c r="D410" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E410">
         <v>12345678</v>
@@ -22546,7 +22546,7 @@
         <v>298</v>
       </c>
       <c r="D411" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E411">
         <v>12345678</v>
@@ -22691,7 +22691,7 @@
         <v>298</v>
       </c>
       <c r="D416" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E416">
         <v>12345678</v>
@@ -22720,7 +22720,7 @@
         <v>298</v>
       </c>
       <c r="D417" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E417">
         <v>12345678</v>
@@ -22865,7 +22865,7 @@
         <v>298</v>
       </c>
       <c r="D422" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E422">
         <v>12345678</v>
@@ -22894,7 +22894,7 @@
         <v>298</v>
       </c>
       <c r="D423" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E423">
         <v>12345678</v>
@@ -23039,7 +23039,7 @@
         <v>298</v>
       </c>
       <c r="D428" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E428">
         <v>12345678</v>
@@ -23068,7 +23068,7 @@
         <v>298</v>
       </c>
       <c r="D429" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E429">
         <v>12345678</v>
@@ -23213,7 +23213,7 @@
         <v>298</v>
       </c>
       <c r="D434" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E434">
         <v>12345678</v>
@@ -23242,7 +23242,7 @@
         <v>298</v>
       </c>
       <c r="D435" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E435">
         <v>12345678</v>
@@ -23387,7 +23387,7 @@
         <v>298</v>
       </c>
       <c r="D440" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E440">
         <v>12345678</v>
@@ -23416,7 +23416,7 @@
         <v>298</v>
       </c>
       <c r="D441" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E441">
         <v>12345678</v>
@@ -23561,7 +23561,7 @@
         <v>298</v>
       </c>
       <c r="D446" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E446">
         <v>12345678</v>
@@ -23590,7 +23590,7 @@
         <v>298</v>
       </c>
       <c r="D447" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E447">
         <v>12345678</v>
@@ -23735,7 +23735,7 @@
         <v>298</v>
       </c>
       <c r="D452" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E452">
         <v>12345678</v>
@@ -23764,7 +23764,7 @@
         <v>298</v>
       </c>
       <c r="D453" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E453">
         <v>12345678</v>
@@ -23909,7 +23909,7 @@
         <v>298</v>
       </c>
       <c r="D458" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E458">
         <v>12345678</v>
@@ -23938,7 +23938,7 @@
         <v>298</v>
       </c>
       <c r="D459" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E459">
         <v>12345678</v>
@@ -24083,7 +24083,7 @@
         <v>298</v>
       </c>
       <c r="D464" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E464">
         <v>12345678</v>
@@ -24112,7 +24112,7 @@
         <v>298</v>
       </c>
       <c r="D465" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E465">
         <v>12345678</v>
@@ -24257,7 +24257,7 @@
         <v>298</v>
       </c>
       <c r="D470" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E470">
         <v>12345678</v>
@@ -24286,7 +24286,7 @@
         <v>298</v>
       </c>
       <c r="D471" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E471">
         <v>12345678</v>
@@ -24431,7 +24431,7 @@
         <v>298</v>
       </c>
       <c r="D476" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E476">
         <v>12345678</v>
@@ -24460,7 +24460,7 @@
         <v>298</v>
       </c>
       <c r="D477" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E477">
         <v>12345678</v>
@@ -24605,7 +24605,7 @@
         <v>298</v>
       </c>
       <c r="D482" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E482">
         <v>12345678</v>
@@ -24634,7 +24634,7 @@
         <v>298</v>
       </c>
       <c r="D483" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E483">
         <v>12345678</v>
@@ -24779,7 +24779,7 @@
         <v>298</v>
       </c>
       <c r="D488" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E488">
         <v>12345678</v>
@@ -24808,7 +24808,7 @@
         <v>298</v>
       </c>
       <c r="D489" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E489">
         <v>12345678</v>
@@ -24953,7 +24953,7 @@
         <v>298</v>
       </c>
       <c r="D494" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E494">
         <v>12345678</v>
@@ -24982,7 +24982,7 @@
         <v>298</v>
       </c>
       <c r="D495" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E495">
         <v>12345678</v>
@@ -25127,7 +25127,7 @@
         <v>298</v>
       </c>
       <c r="D500" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E500">
         <v>12345678</v>
@@ -25156,7 +25156,7 @@
         <v>298</v>
       </c>
       <c r="D501" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E501">
         <v>12345678</v>
@@ -25301,7 +25301,7 @@
         <v>298</v>
       </c>
       <c r="D506" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E506">
         <v>12345678</v>
@@ -25330,7 +25330,7 @@
         <v>298</v>
       </c>
       <c r="D507" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E507">
         <v>12345678</v>
@@ -25475,7 +25475,7 @@
         <v>298</v>
       </c>
       <c r="D512" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E512">
         <v>12345678</v>
@@ -25504,7 +25504,7 @@
         <v>298</v>
       </c>
       <c r="D513" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E513">
         <v>12345678</v>
@@ -25649,7 +25649,7 @@
         <v>298</v>
       </c>
       <c r="D518" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E518">
         <v>12345678</v>
@@ -25678,7 +25678,7 @@
         <v>298</v>
       </c>
       <c r="D519" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E519">
         <v>12345678</v>
@@ -25823,7 +25823,7 @@
         <v>298</v>
       </c>
       <c r="D524" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E524">
         <v>12345678</v>
@@ -25852,7 +25852,7 @@
         <v>298</v>
       </c>
       <c r="D525" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E525">
         <v>12345678</v>
@@ -25997,7 +25997,7 @@
         <v>298</v>
       </c>
       <c r="D530" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E530">
         <v>12345678</v>
@@ -26026,7 +26026,7 @@
         <v>298</v>
       </c>
       <c r="D531" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E531">
         <v>12345678</v>
@@ -26171,7 +26171,7 @@
         <v>298</v>
       </c>
       <c r="D536" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E536">
         <v>12345678</v>
@@ -26200,7 +26200,7 @@
         <v>298</v>
       </c>
       <c r="D537" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E537">
         <v>12345678</v>
@@ -26345,7 +26345,7 @@
         <v>298</v>
       </c>
       <c r="D542" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E542">
         <v>12345678</v>
@@ -26374,7 +26374,7 @@
         <v>298</v>
       </c>
       <c r="D543" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E543">
         <v>12345678</v>
@@ -26519,7 +26519,7 @@
         <v>298</v>
       </c>
       <c r="D548" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E548">
         <v>12345678</v>
@@ -26548,7 +26548,7 @@
         <v>298</v>
       </c>
       <c r="D549" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E549">
         <v>12345678</v>
@@ -26693,7 +26693,7 @@
         <v>298</v>
       </c>
       <c r="D554" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E554">
         <v>12345678</v>
@@ -26722,7 +26722,7 @@
         <v>298</v>
       </c>
       <c r="D555" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E555">
         <v>12345678</v>
@@ -26867,7 +26867,7 @@
         <v>298</v>
       </c>
       <c r="D560" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E560">
         <v>12345678</v>
@@ -26896,7 +26896,7 @@
         <v>298</v>
       </c>
       <c r="D561" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E561">
         <v>12345678</v>
@@ -27041,7 +27041,7 @@
         <v>298</v>
       </c>
       <c r="D566" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E566">
         <v>12345678</v>
@@ -27070,7 +27070,7 @@
         <v>298</v>
       </c>
       <c r="D567" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E567">
         <v>12345678</v>
@@ -27215,7 +27215,7 @@
         <v>298</v>
       </c>
       <c r="D572" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E572">
         <v>12345678</v>
@@ -27244,7 +27244,7 @@
         <v>298</v>
       </c>
       <c r="D573" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E573">
         <v>12345678</v>
@@ -27389,7 +27389,7 @@
         <v>298</v>
       </c>
       <c r="D578" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E578">
         <v>12345678</v>
@@ -27418,7 +27418,7 @@
         <v>298</v>
       </c>
       <c r="D579" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E579">
         <v>12345678</v>
@@ -27563,7 +27563,7 @@
         <v>298</v>
       </c>
       <c r="D584" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E584">
         <v>12345678</v>
@@ -27592,7 +27592,7 @@
         <v>298</v>
       </c>
       <c r="D585" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E585">
         <v>12345678</v>
@@ -27737,7 +27737,7 @@
         <v>298</v>
       </c>
       <c r="D590" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E590">
         <v>12345678</v>
@@ -27766,7 +27766,7 @@
         <v>298</v>
       </c>
       <c r="D591" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E591">
         <v>12345678</v>
@@ -27911,7 +27911,7 @@
         <v>298</v>
       </c>
       <c r="D596" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E596">
         <v>12345678</v>
@@ -27940,7 +27940,7 @@
         <v>298</v>
       </c>
       <c r="D597" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E597">
         <v>12345678</v>
@@ -28085,7 +28085,7 @@
         <v>298</v>
       </c>
       <c r="D602" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E602">
         <v>12345678</v>
@@ -28114,7 +28114,7 @@
         <v>298</v>
       </c>
       <c r="D603" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E603">
         <v>12345678</v>
@@ -28259,7 +28259,7 @@
         <v>298</v>
       </c>
       <c r="D608" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E608">
         <v>12345678</v>
@@ -28288,7 +28288,7 @@
         <v>298</v>
       </c>
       <c r="D609" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E609">
         <v>12345678</v>
@@ -28433,7 +28433,7 @@
         <v>298</v>
       </c>
       <c r="D614" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E614">
         <v>12345678</v>
@@ -28462,7 +28462,7 @@
         <v>298</v>
       </c>
       <c r="D615" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E615">
         <v>12345678</v>
@@ -28607,7 +28607,7 @@
         <v>298</v>
       </c>
       <c r="D620" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E620">
         <v>12345678</v>
@@ -28636,7 +28636,7 @@
         <v>298</v>
       </c>
       <c r="D621" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E621">
         <v>12345678</v>
@@ -28781,7 +28781,7 @@
         <v>298</v>
       </c>
       <c r="D626" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E626">
         <v>12345678</v>
@@ -28810,7 +28810,7 @@
         <v>298</v>
       </c>
       <c r="D627" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E627">
         <v>12345678</v>
@@ -28955,7 +28955,7 @@
         <v>298</v>
       </c>
       <c r="D632" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E632">
         <v>12345678</v>
@@ -28984,7 +28984,7 @@
         <v>298</v>
       </c>
       <c r="D633" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E633">
         <v>12345678</v>
@@ -29129,7 +29129,7 @@
         <v>298</v>
       </c>
       <c r="D638" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E638">
         <v>12345678</v>
@@ -29158,7 +29158,7 @@
         <v>298</v>
       </c>
       <c r="D639" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E639">
         <v>12345678</v>
@@ -29303,7 +29303,7 @@
         <v>298</v>
       </c>
       <c r="D644" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E644">
         <v>12345678</v>
@@ -29332,7 +29332,7 @@
         <v>298</v>
       </c>
       <c r="D645" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E645">
         <v>12345678</v>
@@ -29477,7 +29477,7 @@
         <v>298</v>
       </c>
       <c r="D650" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E650">
         <v>12345678</v>
@@ -29506,7 +29506,7 @@
         <v>298</v>
       </c>
       <c r="D651" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E651">
         <v>12345678</v>
@@ -29651,7 +29651,7 @@
         <v>298</v>
       </c>
       <c r="D656" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E656">
         <v>12345678</v>
@@ -29680,7 +29680,7 @@
         <v>298</v>
       </c>
       <c r="D657" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E657">
         <v>12345678</v>
@@ -29825,7 +29825,7 @@
         <v>298</v>
       </c>
       <c r="D662" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E662">
         <v>12345678</v>
@@ -29854,7 +29854,7 @@
         <v>298</v>
       </c>
       <c r="D663" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E663">
         <v>12345678</v>
@@ -29999,7 +29999,7 @@
         <v>298</v>
       </c>
       <c r="D668" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E668">
         <v>12345678</v>
@@ -30028,7 +30028,7 @@
         <v>298</v>
       </c>
       <c r="D669" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E669">
         <v>12345678</v>
@@ -30173,7 +30173,7 @@
         <v>298</v>
       </c>
       <c r="D674" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E674">
         <v>12345678</v>
@@ -30202,7 +30202,7 @@
         <v>298</v>
       </c>
       <c r="D675" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E675">
         <v>12345678</v>
@@ -30347,7 +30347,7 @@
         <v>298</v>
       </c>
       <c r="D680" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E680">
         <v>12345678</v>
@@ -30376,7 +30376,7 @@
         <v>298</v>
       </c>
       <c r="D681" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E681">
         <v>12345678</v>
@@ -30521,7 +30521,7 @@
         <v>298</v>
       </c>
       <c r="D686" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E686">
         <v>12345678</v>
@@ -30550,7 +30550,7 @@
         <v>298</v>
       </c>
       <c r="D687" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E687">
         <v>12345678</v>
@@ -30695,7 +30695,7 @@
         <v>298</v>
       </c>
       <c r="D692" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E692">
         <v>12345678</v>
@@ -30724,7 +30724,7 @@
         <v>298</v>
       </c>
       <c r="D693" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E693">
         <v>12345678</v>
@@ -30869,7 +30869,7 @@
         <v>298</v>
       </c>
       <c r="D698" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E698">
         <v>12345678</v>
@@ -30898,7 +30898,7 @@
         <v>298</v>
       </c>
       <c r="D699" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E699">
         <v>12345678</v>
@@ -31043,7 +31043,7 @@
         <v>298</v>
       </c>
       <c r="D704" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E704">
         <v>12345678</v>
@@ -31072,7 +31072,7 @@
         <v>298</v>
       </c>
       <c r="D705" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E705">
         <v>12345678</v>
@@ -31217,7 +31217,7 @@
         <v>298</v>
       </c>
       <c r="D710" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E710">
         <v>12345678</v>
@@ -31246,7 +31246,7 @@
         <v>298</v>
       </c>
       <c r="D711" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E711">
         <v>12345678</v>
@@ -31391,7 +31391,7 @@
         <v>298</v>
       </c>
       <c r="D716" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E716">
         <v>12345678</v>
@@ -31420,7 +31420,7 @@
         <v>298</v>
       </c>
       <c r="D717" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E717">
         <v>12345678</v>
@@ -31565,7 +31565,7 @@
         <v>298</v>
       </c>
       <c r="D722" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E722">
         <v>12345678</v>
@@ -31594,7 +31594,7 @@
         <v>298</v>
       </c>
       <c r="D723" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E723">
         <v>12345678</v>
@@ -31739,7 +31739,7 @@
         <v>298</v>
       </c>
       <c r="D728" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E728">
         <v>12345678</v>
@@ -31768,7 +31768,7 @@
         <v>298</v>
       </c>
       <c r="D729" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E729">
         <v>12345678</v>
@@ -31913,7 +31913,7 @@
         <v>298</v>
       </c>
       <c r="D734" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E734">
         <v>12345678</v>
@@ -31942,7 +31942,7 @@
         <v>298</v>
       </c>
       <c r="D735" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E735">
         <v>12345678</v>
@@ -32087,7 +32087,7 @@
         <v>298</v>
       </c>
       <c r="D740" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E740">
         <v>12345678</v>
@@ -32116,7 +32116,7 @@
         <v>298</v>
       </c>
       <c r="D741" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E741">
         <v>12345678</v>
@@ -32261,7 +32261,7 @@
         <v>298</v>
       </c>
       <c r="D746" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E746">
         <v>12345678</v>
@@ -32290,7 +32290,7 @@
         <v>298</v>
       </c>
       <c r="D747" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E747">
         <v>12345678</v>
@@ -32435,7 +32435,7 @@
         <v>298</v>
       </c>
       <c r="D752" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E752">
         <v>12345678</v>
@@ -32464,7 +32464,7 @@
         <v>298</v>
       </c>
       <c r="D753" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E753">
         <v>12345678</v>
@@ -32609,7 +32609,7 @@
         <v>298</v>
       </c>
       <c r="D758" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E758">
         <v>12345678</v>
@@ -32638,7 +32638,7 @@
         <v>298</v>
       </c>
       <c r="D759" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E759">
         <v>12345678</v>
@@ -32783,7 +32783,7 @@
         <v>298</v>
       </c>
       <c r="D764" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E764">
         <v>12345678</v>
@@ -32812,7 +32812,7 @@
         <v>298</v>
       </c>
       <c r="D765" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E765">
         <v>12345678</v>
@@ -32957,7 +32957,7 @@
         <v>298</v>
       </c>
       <c r="D770" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E770">
         <v>12345678</v>
@@ -32986,7 +32986,7 @@
         <v>298</v>
       </c>
       <c r="D771" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E771">
         <v>12345678</v>
@@ -33131,7 +33131,7 @@
         <v>298</v>
       </c>
       <c r="D776" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E776">
         <v>12345678</v>
@@ -33160,7 +33160,7 @@
         <v>298</v>
       </c>
       <c r="D777" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E777">
         <v>12345678</v>
@@ -33305,7 +33305,7 @@
         <v>298</v>
       </c>
       <c r="D782" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E782">
         <v>12345678</v>
@@ -33334,7 +33334,7 @@
         <v>298</v>
       </c>
       <c r="D783" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E783">
         <v>12345678</v>
@@ -33479,7 +33479,7 @@
         <v>298</v>
       </c>
       <c r="D788" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E788">
         <v>12345678</v>
@@ -33508,7 +33508,7 @@
         <v>298</v>
       </c>
       <c r="D789" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E789">
         <v>12345678</v>
@@ -33653,7 +33653,7 @@
         <v>298</v>
       </c>
       <c r="D794" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E794">
         <v>12345678</v>
@@ -33682,7 +33682,7 @@
         <v>298</v>
       </c>
       <c r="D795" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E795">
         <v>12345678</v>
@@ -33827,7 +33827,7 @@
         <v>298</v>
       </c>
       <c r="D800" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E800">
         <v>12345678</v>
@@ -33856,7 +33856,7 @@
         <v>298</v>
       </c>
       <c r="D801" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E801">
         <v>12345678</v>
@@ -34001,7 +34001,7 @@
         <v>298</v>
       </c>
       <c r="D806" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E806">
         <v>12345678</v>
@@ -34030,7 +34030,7 @@
         <v>298</v>
       </c>
       <c r="D807" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E807">
         <v>12345678</v>
@@ -34175,7 +34175,7 @@
         <v>298</v>
       </c>
       <c r="D812" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E812">
         <v>12345678</v>
@@ -34204,7 +34204,7 @@
         <v>298</v>
       </c>
       <c r="D813" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E813">
         <v>12345678</v>
@@ -34349,7 +34349,7 @@
         <v>298</v>
       </c>
       <c r="D818" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E818">
         <v>12345678</v>
@@ -34378,7 +34378,7 @@
         <v>298</v>
       </c>
       <c r="D819" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E819">
         <v>12345678</v>
@@ -34523,7 +34523,7 @@
         <v>298</v>
       </c>
       <c r="D824" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E824">
         <v>12345678</v>
@@ -34552,7 +34552,7 @@
         <v>298</v>
       </c>
       <c r="D825" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E825">
         <v>12345678</v>
@@ -34697,7 +34697,7 @@
         <v>298</v>
       </c>
       <c r="D830" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E830">
         <v>12345678</v>
@@ -34726,7 +34726,7 @@
         <v>298</v>
       </c>
       <c r="D831" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E831">
         <v>12345678</v>
@@ -34871,7 +34871,7 @@
         <v>298</v>
       </c>
       <c r="D836" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E836">
         <v>12345678</v>
@@ -34900,7 +34900,7 @@
         <v>298</v>
       </c>
       <c r="D837" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E837">
         <v>12345678</v>
@@ -35045,7 +35045,7 @@
         <v>298</v>
       </c>
       <c r="D842" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E842">
         <v>12345678</v>
@@ -35074,7 +35074,7 @@
         <v>298</v>
       </c>
       <c r="D843" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E843">
         <v>12345678</v>
@@ -35219,7 +35219,7 @@
         <v>298</v>
       </c>
       <c r="D848" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E848">
         <v>12345678</v>
@@ -35248,7 +35248,7 @@
         <v>298</v>
       </c>
       <c r="D849" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E849">
         <v>12345678</v>
@@ -35393,7 +35393,7 @@
         <v>298</v>
       </c>
       <c r="D854" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E854">
         <v>12345678</v>
@@ -35422,7 +35422,7 @@
         <v>298</v>
       </c>
       <c r="D855" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E855">
         <v>12345678</v>
@@ -35567,7 +35567,7 @@
         <v>298</v>
       </c>
       <c r="D860" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E860">
         <v>12345678</v>
@@ -35596,7 +35596,7 @@
         <v>298</v>
       </c>
       <c r="D861" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E861">
         <v>12345678</v>
@@ -35741,7 +35741,7 @@
         <v>298</v>
       </c>
       <c r="D866" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E866">
         <v>12345678</v>
@@ -35770,7 +35770,7 @@
         <v>298</v>
       </c>
       <c r="D867" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E867">
         <v>12345678</v>
@@ -35915,7 +35915,7 @@
         <v>298</v>
       </c>
       <c r="D872" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E872">
         <v>12345678</v>
@@ -35944,7 +35944,7 @@
         <v>298</v>
       </c>
       <c r="D873" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E873">
         <v>12345678</v>
@@ -36089,7 +36089,7 @@
         <v>298</v>
       </c>
       <c r="D878" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E878">
         <v>12345678</v>
@@ -36118,7 +36118,7 @@
         <v>298</v>
       </c>
       <c r="D879" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E879">
         <v>12345678</v>
@@ -36263,7 +36263,7 @@
         <v>298</v>
       </c>
       <c r="D884" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E884">
         <v>12345678</v>
@@ -36292,7 +36292,7 @@
         <v>298</v>
       </c>
       <c r="D885" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E885">
         <v>12345678</v>
@@ -36437,7 +36437,7 @@
         <v>298</v>
       </c>
       <c r="D890" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E890">
         <v>12345678</v>
@@ -36466,7 +36466,7 @@
         <v>298</v>
       </c>
       <c r="D891" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E891">
         <v>12345678</v>
@@ -36611,7 +36611,7 @@
         <v>298</v>
       </c>
       <c r="D896" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E896">
         <v>12345678</v>
@@ -36640,7 +36640,7 @@
         <v>298</v>
       </c>
       <c r="D897" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E897">
         <v>12345678</v>
@@ -36785,7 +36785,7 @@
         <v>298</v>
       </c>
       <c r="D902" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E902">
         <v>12345678</v>
@@ -36814,7 +36814,7 @@
         <v>298</v>
       </c>
       <c r="D903" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E903">
         <v>12345678</v>
@@ -36959,7 +36959,7 @@
         <v>298</v>
       </c>
       <c r="D908" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E908">
         <v>12345678</v>
@@ -36988,7 +36988,7 @@
         <v>298</v>
       </c>
       <c r="D909" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E909">
         <v>12345678</v>
@@ -37133,7 +37133,7 @@
         <v>298</v>
       </c>
       <c r="D914" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E914">
         <v>12345678</v>
@@ -37162,7 +37162,7 @@
         <v>298</v>
       </c>
       <c r="D915" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E915">
         <v>12345678</v>
@@ -37307,7 +37307,7 @@
         <v>298</v>
       </c>
       <c r="D920" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E920">
         <v>12345678</v>
@@ -37336,7 +37336,7 @@
         <v>298</v>
       </c>
       <c r="D921" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E921">
         <v>12345678</v>
@@ -37481,7 +37481,7 @@
         <v>298</v>
       </c>
       <c r="D926" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E926">
         <v>12345678</v>
@@ -37510,7 +37510,7 @@
         <v>298</v>
       </c>
       <c r="D927" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E927">
         <v>12345678</v>
@@ -37655,7 +37655,7 @@
         <v>298</v>
       </c>
       <c r="D932" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E932">
         <v>12345678</v>
@@ -37684,7 +37684,7 @@
         <v>298</v>
       </c>
       <c r="D933" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E933">
         <v>12345678</v>
@@ -37829,7 +37829,7 @@
         <v>298</v>
       </c>
       <c r="D938" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E938">
         <v>12345678</v>
@@ -37858,7 +37858,7 @@
         <v>298</v>
       </c>
       <c r="D939" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E939">
         <v>12345678</v>
@@ -38003,7 +38003,7 @@
         <v>298</v>
       </c>
       <c r="D944" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E944">
         <v>12345678</v>
@@ -38032,7 +38032,7 @@
         <v>298</v>
       </c>
       <c r="D945" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E945">
         <v>12345678</v>
@@ -38177,7 +38177,7 @@
         <v>298</v>
       </c>
       <c r="D950" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E950">
         <v>12345678</v>
@@ -38206,7 +38206,7 @@
         <v>298</v>
       </c>
       <c r="D951" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E951">
         <v>12345678</v>
@@ -38351,7 +38351,7 @@
         <v>298</v>
       </c>
       <c r="D956" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E956">
         <v>12345678</v>
@@ -38380,7 +38380,7 @@
         <v>298</v>
       </c>
       <c r="D957" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E957">
         <v>12345678</v>
@@ -38525,7 +38525,7 @@
         <v>298</v>
       </c>
       <c r="D962" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E962">
         <v>12345678</v>
@@ -38554,7 +38554,7 @@
         <v>298</v>
       </c>
       <c r="D963" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E963">
         <v>12345678</v>
@@ -38699,7 +38699,7 @@
         <v>298</v>
       </c>
       <c r="D968" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E968">
         <v>12345678</v>
@@ -38728,7 +38728,7 @@
         <v>298</v>
       </c>
       <c r="D969" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E969">
         <v>12345678</v>
@@ -38873,7 +38873,7 @@
         <v>298</v>
       </c>
       <c r="D974" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E974">
         <v>12345678</v>
@@ -38902,7 +38902,7 @@
         <v>298</v>
       </c>
       <c r="D975" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E975">
         <v>12345678</v>
@@ -39047,7 +39047,7 @@
         <v>298</v>
       </c>
       <c r="D980" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E980">
         <v>12345678</v>
@@ -39076,7 +39076,7 @@
         <v>298</v>
       </c>
       <c r="D981" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E981">
         <v>12345678</v>
@@ -39221,7 +39221,7 @@
         <v>298</v>
       </c>
       <c r="D986" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E986">
         <v>12345678</v>
@@ -39250,7 +39250,7 @@
         <v>298</v>
       </c>
       <c r="D987" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E987">
         <v>12345678</v>
@@ -39395,7 +39395,7 @@
         <v>298</v>
       </c>
       <c r="D992" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E992">
         <v>12345678</v>
@@ -39424,7 +39424,7 @@
         <v>298</v>
       </c>
       <c r="D993" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E993">
         <v>12345678</v>
@@ -39569,7 +39569,7 @@
         <v>298</v>
       </c>
       <c r="D998" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E998">
         <v>12345678</v>
@@ -39598,7 +39598,7 @@
         <v>298</v>
       </c>
       <c r="D999" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E999">
         <v>12345678</v>
@@ -39743,7 +39743,7 @@
         <v>298</v>
       </c>
       <c r="D1004" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1004">
         <v>12345678</v>
@@ -39772,7 +39772,7 @@
         <v>298</v>
       </c>
       <c r="D1005" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1005">
         <v>12345678</v>
@@ -39917,7 +39917,7 @@
         <v>298</v>
       </c>
       <c r="D1010" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1010">
         <v>12345678</v>
@@ -39946,7 +39946,7 @@
         <v>298</v>
       </c>
       <c r="D1011" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1011">
         <v>12345678</v>
@@ -40091,7 +40091,7 @@
         <v>298</v>
       </c>
       <c r="D1016" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1016">
         <v>12345678</v>
@@ -40120,7 +40120,7 @@
         <v>298</v>
       </c>
       <c r="D1017" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1017">
         <v>12345678</v>
@@ -40265,7 +40265,7 @@
         <v>298</v>
       </c>
       <c r="D1022" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1022">
         <v>12345678</v>
@@ -40294,7 +40294,7 @@
         <v>298</v>
       </c>
       <c r="D1023" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1023">
         <v>12345678</v>
@@ -40439,7 +40439,7 @@
         <v>298</v>
       </c>
       <c r="D1028" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1028">
         <v>12345678</v>
@@ -40468,7 +40468,7 @@
         <v>298</v>
       </c>
       <c r="D1029" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1029">
         <v>12345678</v>
@@ -40613,7 +40613,7 @@
         <v>298</v>
       </c>
       <c r="D1034" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1034">
         <v>12345678</v>
@@ -40642,7 +40642,7 @@
         <v>298</v>
       </c>
       <c r="D1035" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1035">
         <v>12345678</v>
@@ -40787,7 +40787,7 @@
         <v>298</v>
       </c>
       <c r="D1040" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1040">
         <v>12345678</v>
@@ -40816,7 +40816,7 @@
         <v>298</v>
       </c>
       <c r="D1041" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1041">
         <v>12345678</v>
@@ -40961,7 +40961,7 @@
         <v>298</v>
       </c>
       <c r="D1046" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1046">
         <v>12345678</v>
@@ -40990,7 +40990,7 @@
         <v>298</v>
       </c>
       <c r="D1047" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1047">
         <v>12345678</v>
@@ -41135,7 +41135,7 @@
         <v>298</v>
       </c>
       <c r="D1052" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1052">
         <v>12345678</v>
@@ -41164,7 +41164,7 @@
         <v>298</v>
       </c>
       <c r="D1053" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1053">
         <v>12345678</v>
@@ -41309,7 +41309,7 @@
         <v>298</v>
       </c>
       <c r="D1058" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1058">
         <v>12345678</v>
@@ -41338,7 +41338,7 @@
         <v>298</v>
       </c>
       <c r="D1059" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1059">
         <v>12345678</v>
@@ -41483,7 +41483,7 @@
         <v>298</v>
       </c>
       <c r="D1064" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1064">
         <v>12345678</v>
@@ -41512,7 +41512,7 @@
         <v>298</v>
       </c>
       <c r="D1065" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1065">
         <v>12345678</v>
@@ -41657,7 +41657,7 @@
         <v>298</v>
       </c>
       <c r="D1070" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1070">
         <v>12345678</v>
@@ -41686,7 +41686,7 @@
         <v>298</v>
       </c>
       <c r="D1071" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1071">
         <v>12345678</v>
@@ -41831,7 +41831,7 @@
         <v>298</v>
       </c>
       <c r="D1076" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1076">
         <v>12345678</v>
@@ -41860,7 +41860,7 @@
         <v>298</v>
       </c>
       <c r="D1077" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1077">
         <v>12345678</v>
@@ -42005,7 +42005,7 @@
         <v>298</v>
       </c>
       <c r="D1082" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1082">
         <v>12345678</v>
@@ -42034,7 +42034,7 @@
         <v>298</v>
       </c>
       <c r="D1083" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1083">
         <v>12345678</v>
@@ -42179,7 +42179,7 @@
         <v>298</v>
       </c>
       <c r="D1088" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1088">
         <v>12345678</v>
@@ -42208,7 +42208,7 @@
         <v>298</v>
       </c>
       <c r="D1089" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1089">
         <v>12345678</v>
@@ -42353,7 +42353,7 @@
         <v>298</v>
       </c>
       <c r="D1094" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1094">
         <v>12345678</v>
@@ -42382,7 +42382,7 @@
         <v>298</v>
       </c>
       <c r="D1095" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1095">
         <v>12345678</v>
@@ -42527,7 +42527,7 @@
         <v>298</v>
       </c>
       <c r="D1100" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1100">
         <v>12345678</v>
@@ -42556,7 +42556,7 @@
         <v>298</v>
       </c>
       <c r="D1101" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E1101">
         <v>12345678</v>
